--- a/results/ai_run/682_z08/5_quantification/682_z08_quantification.xlsx
+++ b/results/ai_run/682_z08/5_quantification/682_z08_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15.3333</v>
+        <v>13.6667</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>5.172</v>
+        <v>5.8523</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.3858</v>
+        <v>5.5684</v>
       </c>
       <c r="D25" t="n">
-        <v>6.285</v>
+        <v>5.4625</v>
       </c>
       <c r="E25" t="n">
-        <v>1.1923</v>
+        <v>1.2117</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
         <v>461</v>
@@ -2631,7 +2631,7 @@
         <v>0.037759</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2091</v>
+        <v>2.0792</v>
       </c>
       <c r="Z2" t="n">
         <v>408</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>506</v>
@@ -2738,7 +2738,7 @@
         <v>0.05768212</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.3858</v>
+        <v>5.9601</v>
       </c>
       <c r="Z3" t="n">
         <v>491</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" t="n">
         <v>512</v>
@@ -2845,7 +2845,7 @@
         <v>0.04343885</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.3705</v>
+        <v>6.052</v>
       </c>
       <c r="Z4" t="n">
         <v>491</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>481</v>
@@ -3059,7 +3059,7 @@
         <v>0.0454615</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.0025</v>
+        <v>4.7162</v>
       </c>
       <c r="Z6" t="n">
         <v>443</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M7" t="n">
         <v>500</v>
@@ -3166,7 +3166,7 @@
         <v>0.05963039</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.2235</v>
+        <v>5.4176</v>
       </c>
       <c r="Z7" t="n">
         <v>472</v>
@@ -3234,7 +3234,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
         <v>212</v>
@@ -3273,7 +3273,7 @@
         <v>0.04542021</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.5251</v>
+        <v>3.2625</v>
       </c>
       <c r="Z8" t="n">
         <v>174</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M9" t="n">
         <v>685</v>
@@ -3380,7 +3380,7 @@
         <v>0.05109883</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.0694</v>
+        <v>5.4625</v>
       </c>
       <c r="Z9" t="n">
         <v>605</v>
@@ -3555,7 +3555,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>341</v>
@@ -3594,7 +3594,7 @@
         <v>0.03223871</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.8787</v>
+        <v>3.2525</v>
       </c>
       <c r="Z11" t="n">
         <v>278</v>
@@ -3641,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
         <v>113</v>
@@ -3680,7 +3680,7 @@
         <v>0.01704003</v>
       </c>
       <c r="Y12" t="n">
-        <v>9.0044</v>
+        <v>7.718</v>
       </c>
       <c r="Z12" t="n">
         <v>83</v>
